--- a/plantillas/23.xlsx
+++ b/plantillas/23.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$2</definedName>
     <definedName name="MARCA_2">Listas!$E$2:$E$5</definedName>
     <definedName name="MARCA_3">Listas!$F$2:$F$2</definedName>
     <definedName name="MARCA_4">Listas!$G$2:$G$2</definedName>
-    <definedName name="MARCA_5">Listas!$H$2:$H$3</definedName>
+    <definedName name="MARCA_5">Listas!$H$2:$H$2</definedName>
     <definedName name="MARCA_6">Listas!$I$2:$I$4</definedName>
     <definedName name="MARCA_7">Listas!$J$2:$J$4</definedName>
     <definedName name="MARCA_8">Listas!$K$2:$K$3</definedName>
@@ -26,17 +26,17 @@
     <definedName name="MARCA_12">Listas!$O$2:$O$6</definedName>
     <definedName name="MARCA_13">Listas!$P$2:$P$5</definedName>
     <definedName name="MARCA_14">Listas!$Q$2:$Q$2</definedName>
-    <definedName name="MARCA_15">Listas!$R$2:$R$5</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$18</definedName>
+    <definedName name="MARCA_15">Listas!$R$2:$R$6</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$19</definedName>
     <definedName name="MARCA_17">Listas!$T$2:$T$2</definedName>
-    <definedName name="MARCA_18">Listas!$U$2:$U$15</definedName>
+    <definedName name="MARCA_18">Listas!$U$2:$U$17</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$4</definedName>
     <definedName name="MARCA_20">Listas!$W$2:$W$3</definedName>
     <definedName name="MARCA_21">Listas!$X$2:$X$7</definedName>
     <definedName name="MARCA_22">Listas!$Y$2:$Y$2</definedName>
-    <definedName name="MARCA_23">Listas!$Z$2:$Z$4</definedName>
-    <definedName name="MARCA_24">Listas!$AA$2:$AA$5</definedName>
-    <definedName name="MARCA_25">Listas!$AB$2:$AB$7</definedName>
+    <definedName name="MARCA_23">Listas!$Z$2:$Z$3</definedName>
+    <definedName name="MARCA_24">Listas!$AA$2:$AA$4</definedName>
+    <definedName name="MARCA_25">Listas!$AB$2:$AB$6</definedName>
     <definedName name="MARCA_26">Listas!$AC$2:$AC$7</definedName>
     <definedName name="MARCA_27">Listas!$AD$2:$AD$3</definedName>
     <definedName name="MARCA_28">Listas!$AE$2:$AE$3</definedName>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>SUPER GATO 1.5KG · 93500000800</t>
+          <t>SUPER GATO 500GRS · 93500000700</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -8623,11 +8623,6 @@
           <t>ASCAN ADULTOS 1KG · 93513390000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
@@ -8695,7 +8690,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>SUPER GATO 500GRS · 93500000700</t>
+          <t>SUPER GATO 8KG · 93500000900</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -8799,11 +8794,6 @@
           <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>SUPER GATO 8KG · 93500000900</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>ROCKY ADULTOS 500G · 93500000341</t>
@@ -8811,7 +8801,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -8880,14 +8870,9 @@
           <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
-        </is>
-      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -8922,6 +8907,11 @@
           <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
@@ -8939,7 +8929,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -8984,11 +8974,6 @@
           <t>SNACK BEGGIN STRIPS BACON 85G · 90401200000</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>TETRAMIN HOJUELAS PEZ TROPICAL1OZ · 90410980000</t>
@@ -9123,7 +9108,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
     </row>
@@ -9140,12 +9125,12 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9147,12 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9169,12 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9191,12 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9213,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
     </row>
@@ -9231,6 +9226,11 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>MARCA_18</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
     </row>
@@ -9553,36 +9553,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAT CHOW DEFENSE PLUS PESCADO 1.5KG · 90408400000</t>
+          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>90408400000</t>
+          <t>93511170000</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CAT CHOW</t>
+          <t>CHICKEN SOUP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CS ALIMENTO EN LATA P/ADULTO 13OZ · 93511170000</t>
+          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>93511170000</t>
+          <t>93514480000</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9593,16 +9593,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CS GRAIN FREE SALMON/PERRO 22 LB · 93514480000</t>
+          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93514480000</t>
+          <t>93511270000</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -9613,32 +9613,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CS SNACK CRUNCHY POLLO P/PERRO 12OZ · 93511270000</t>
+          <t>DOG CHOW ADULT RZ PEQUENA 2KG · 90410400000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>93511270000</t>
+          <t>90410400000</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHICKEN SOUP</t>
+          <t>DOG CHOW</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULT RZ PEQUENA 2KG · 90410400000</t>
+          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>90410400000</t>
+          <t>93512370000</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -9653,16 +9653,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DOG CHOW ADULTO 2KG · 93512370000</t>
+          <t>DOG CHOW CACHORRO RAZA MD/GRD 2KG · 93512530000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>93512370000</t>
+          <t>93512530000</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9673,36 +9673,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DOG CHOW CACHORRO RAZA MD/GRD 2KG · 93512530000</t>
+          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>93512530000</t>
+          <t>90311050000</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DOG CHOW</t>
+          <t>ESBILAC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ESBILAC LECHE EN POLVO 12 ONZ · 90311050000</t>
+          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90311050000</t>
+          <t>90401410000</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9713,36 +9713,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LECHE ESBILAC P GATOS 6 OZ. · 90401410000</t>
+          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90401410000</t>
+          <t>90038530000</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>FELIX</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FELIX DELICIAS DE LA GRANJA ADULTO 1KG M · 90038530000</t>
+          <t>FELIX GATITOS 500G MX · 90038510000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90038530000</t>
+          <t>90038510000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9753,12 +9753,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FELIX GATITOS 500G MX · 90038510000</t>
+          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90038510000</t>
+          <t>90038550000</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -9773,16 +9773,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FELIX MEGAMIX ADULTO 500G MX · 90038550000</t>
+          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90038550000</t>
+          <t>93502660000</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9793,16 +9793,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FELIX PATE PAVO Y MENUDENCIAS 156G · 93502660000</t>
+          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>93502660000</t>
+          <t>93502640000</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -9813,16 +9813,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FELIX PATE PESCADO Y ATUN 156G · 93502640000</t>
+          <t>FELIX PATE SALMON 156G · 93502650000</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>93502640000</t>
+          <t>93502650000</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9833,36 +9833,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FELIX PATE SALMON 156G · 93502650000</t>
+          <t>GATI ATUN 2.2LB · 93519180000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>93502650000</t>
+          <t>93519180000</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>GATI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GATI ATUN 2.2LB · 93519180000</t>
+          <t>GATI GATITOS 2.2LB · 93519200000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>93519180000</t>
+          <t>93519200000</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9873,12 +9873,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GATI GATITOS 2.2LB · 93519200000</t>
+          <t>GATI MAR Y TIERRA 2.2LB · 93519160000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>93519200000</t>
+          <t>93519160000</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -9893,16 +9893,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GATI MAR Y TIERRA 2.2LB · 93519160000</t>
+          <t>GATI MAR Y TIERRA 6.6LB · 93519170000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>93519160000</t>
+          <t>93519170000</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -9913,16 +9913,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GATI MAR Y TIERRA 6.6LB · 93519170000</t>
+          <t>GATI PESCADO 2.2LB · 93519140000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>93519170000</t>
+          <t>93519140000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9933,16 +9933,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GATI PESCADO 2.2LB · 93519140000</t>
+          <t>GATI POLLO 2.2LB · 93519130000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93519140000</t>
+          <t>93519130000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9953,56 +9953,56 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GATI POLLO 2.2LB · 93519130000</t>
+          <t>SEMILLAS DE ALPISTE 100LB · 93501550000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93519130000</t>
+          <t>93501550000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GATI</t>
+          <t>GENÉRICO (granel)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEMILLAS DE ALPISTE 100LB · 93501550000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>93501550000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GENÉRICO (granel)</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10013,16 +10013,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -10033,16 +10033,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -10053,16 +10053,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10073,36 +10073,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>90404930000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
+          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>90404930000</t>
+          <t>90404920000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -10113,16 +10113,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
+          <t>KT FORTI DIET LORO 5 LB · 90407230000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>90404920000</t>
+          <t>90407230000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -10133,16 +10133,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KT FORTI DIET LORO 5 LB · 90407230000</t>
+          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90407230000</t>
+          <t>93500800000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -10153,56 +10153,56 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
+          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93500800000</t>
+          <t>90720740000</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>KORDON</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KORDON VITAMINAS AVES GRANDES 2 OZ · 90720740000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90720740000</t>
+          <t>90409680000</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KORDON</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90409680000</t>
+          <t>90400360000</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10213,16 +10213,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90400360000</t>
+          <t>93513340000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10233,16 +10233,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>93513340000</t>
+          <t>90400340000</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10253,16 +10253,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90400340000</t>
+          <t>93513280000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10513,16 +10513,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>90410830000</t>
+          <t>90410820000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10533,16 +10533,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90415960000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10553,16 +10553,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90410810000</t>
+          <t>90415960000</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10573,16 +10573,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>93510840000</t>
+          <t>90410810000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10593,16 +10593,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>93510840000</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -10613,52 +10613,52 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NV TRANQUILIZANTES PERRO/GATO 1OZ · 90332560000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90332560000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NUTRI-VET</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
+          <t>NV TRANQUILIZANTES PERRO/GATO 1OZ · 90332560000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>93500000429</t>
+          <t>90332560000</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>NUTRI-VET</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
+          <t>NS CACHORRO RZ GDE POLLO Y ARROZ 4LB · 93500000429</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>93500000461</t>
+          <t>93500000429</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -10673,16 +10673,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>NS CACHORRO RZ PQNA Y MED GF 4LB · 93500000461</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>90034090000</t>
+          <t>93500000461</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -10693,16 +10693,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>90033960000</t>
+          <t>90034090000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -10713,12 +10713,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>90034130000</t>
+          <t>90033960000</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -10733,12 +10733,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
+          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>90034160000</t>
+          <t>90034130000</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -10753,16 +10753,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>90033990000</t>
+          <t>90034160000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10773,12 +10773,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>90034210000</t>
+          <t>90033990000</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -10793,12 +10793,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
+          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>90034250000</t>
+          <t>90034210000</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -10813,12 +10813,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
+          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>90034230000</t>
+          <t>90034250000</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -10833,16 +10833,16 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
+          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>93500000479</t>
+          <t>90034230000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10853,12 +10853,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
+          <t>NS GATO Y GATITO POLLO SALMON HIGADO 4 · 93500000479</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>93500000435</t>
+          <t>93500000479</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -10873,16 +10873,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
+          <t>NS LATA CACHORRO RZ PQNA Y MED 5.5OZ · 93500000471</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>93500000445</t>
+          <t>93500000471</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10893,12 +10893,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
+          <t>NS PERRO ADULTO SMB POLLO Y ARROZ 4LB · 93500000422</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>93500000464</t>
+          <t>93500000422</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -10913,12 +10913,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO GDE SABOR VENADO · 93507970000</t>
+          <t>NS PERRO CORDERO Y ARROZ 4LB · 93500000435</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>93507970000</t>
+          <t>93500000435</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -10926,19 +10926,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO TRIPLE P/CACHORRO · 93508370000</t>
+          <t>NS PERRO GF CORDERO Y GUISANTES 4LB · 93500000445</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>93508370000</t>
+          <t>93500000445</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -10946,59 +10946,59 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NYLABONE HUESO WOLF CARNE ASADA · 93508300000</t>
+          <t>NS PERRO GF MARISCOS 4LB · 93500000464</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>93508300000</t>
+          <t>93500000464</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NYLABONE</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OLA CANARIOS 800GRS · 90405520000</t>
+          <t>NYLABONE HUESO GDE SABOR VENADO · 93507970000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>90405520000</t>
+          <t>93507970000</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
+          <t>NYLABONE HUESO TRIPLE P/CACHORRO · 93508370000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>90405540000</t>
+          <t>93508370000</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -11006,83 +11006,83 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
+          <t>NYLABONE HUESO WOLF CARNE ASADA · 93508300000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>90040920000</t>
+          <t>93508300000</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>NYLABONE</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
+          <t>OLA CANARIOS 800GRS · 90405520000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>90040930000</t>
+          <t>90405520000</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
+          <t>OLA FINCHES/ PAJAROS EXOTICOS 800 · 90405540000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>93516230000</t>
+          <t>90405540000</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PURINA</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
+          <t>3 PACK FELIX SURTIDO (3X156G) · 90040920000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>93516200000</t>
+          <t>90040920000</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11093,16 +11093,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
+          <t>4 PACK FELIX SURTIDO (4X85G) · 90040930000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>93516210000</t>
+          <t>90040930000</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11113,16 +11113,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SNACK BEGGIN STRIPS BACON 85G · 90401200000</t>
+          <t>PURINA FELIX ATUN EN SALSA 85G · 93516230000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>90401200000</t>
+          <t>93516230000</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11133,52 +11133,52 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>PURINA FELIX PAVO EN SALSA 85G · 93516200000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93516200000</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SUPER GATO 1.5KG · 93500000800</t>
+          <t>PURINA FELIX PESCADO EN SALSA 85G · 93516210000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>93500000800</t>
+          <t>93516210000</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SUPER GATO 500GRS · 93500000700</t>
+          <t>SNACK BEGGIN STRIPS BACON 85G · 90401200000</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>93500000700</t>
+          <t>90401200000</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -11186,83 +11186,83 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>PURINA</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SUPER GATO 8KG · 93500000900</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>93500000900</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SUPER GATO</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>SUPER GATO 500GRS · 93500000700</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93500000700</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPER GATO</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>SUPER GATO 8KG · 93500000900</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93500000900</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPER GATO</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>90022370000</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11273,16 +11273,16 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11293,32 +11293,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -11333,16 +11333,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11353,16 +11353,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/23.xlsx
+++ b/plantillas/23.xlsx
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/23.xlsx
+++ b/plantillas/23.xlsx
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
